--- a/Excel_export/2025T135_heating120.xlsx
+++ b/Excel_export/2025T135_heating120.xlsx
@@ -1106,16 +1106,16 @@
     <t>UTC timestamp in ISO 8601 format</t>
   </si>
   <si>
-    <t>Raw GPS latitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
+    <t>Raw GPS latitude on this data time axis</t>
   </si>
   <si>
-    <t>Raw GPS longitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
+    <t>Raw GPS longitude on this data time axis</t>
   </si>
   <si>
-    <t>Quality-controlled latitude; interpolated to heating axes when needed</t>
+    <t>Quality-controlled latitude on this data time axis</t>
   </si>
   <si>
-    <t>Quality-controlled longitude; interpolated to heating axes when needed</t>
+    <t>Quality-controlled longitude on this data time axis</t>
   </si>
   <si>
     <t>1=original; 2=interpolated; 3=invalid; 4=edge extrapolated; 5=long-gap filled</t>
@@ -2290,10 +2290,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>84.167500000000004</v>
+        <v>84.154300000000006</v>
       </c>
       <c r="C2" s="0">
-        <v>21.671800000000001</v>
+        <v>21.997399999999999</v>
       </c>
       <c r="D2" s="0">
         <v>84.167500000000004</v>
@@ -3047,10 +3047,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>84.262100000000004</v>
+        <v>84.2303</v>
       </c>
       <c r="C3" s="0">
-        <v>21.2926</v>
+        <v>21.139800000000001</v>
       </c>
       <c r="D3" s="0">
         <v>84.266900000000007</v>
@@ -3804,10 +3804,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>84.262299999999996</v>
+        <v>84.296800000000005</v>
       </c>
       <c r="C4" s="0">
-        <v>21.291599999999999</v>
+        <v>21.399799999999999</v>
       </c>
       <c r="D4" s="0">
         <v>84.276499999999999</v>
@@ -4561,10 +4561,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>84.361800000000002</v>
+        <v>84.363100000000003</v>
       </c>
       <c r="C5" s="0">
-        <v>21.6858</v>
+        <v>21.666</v>
       </c>
       <c r="D5" s="0">
         <v>84.363399999999999</v>
@@ -5318,10 +5318,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>84.415400000000005</v>
+        <v>84.429299999999998</v>
       </c>
       <c r="C6" s="0">
-        <v>22.287600000000001</v>
+        <v>21.938500000000001</v>
       </c>
       <c r="D6" s="0">
         <v>84.415899999999993</v>
@@ -6075,10 +6075,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>84.4756</v>
+        <v>84.495400000000004</v>
       </c>
       <c r="C7" s="0">
-        <v>21.737200000000001</v>
+        <v>22.217600000000001</v>
       </c>
       <c r="D7" s="0">
         <v>84.475800000000007</v>
@@ -6832,10 +6832,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>84.494600000000005</v>
+        <v>84.561400000000006</v>
       </c>
       <c r="C8" s="0">
-        <v>22.2317</v>
+        <v>22.503499999999999</v>
       </c>
       <c r="D8" s="0">
         <v>84.522000000000006</v>
@@ -7589,10 +7589,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>84.602400000000003</v>
+        <v>84.604799999999997</v>
       </c>
       <c r="C9" s="0">
-        <v>21.491499999999998</v>
+        <v>21.447700000000001</v>
       </c>
       <c r="D9" s="0">
         <v>84.605000000000004</v>
@@ -8346,10 +8346,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>84.682100000000005</v>
+        <v>84.684200000000004</v>
       </c>
       <c r="C10" s="0">
-        <v>21.409700000000001</v>
+        <v>21.3706</v>
       </c>
       <c r="D10" s="0">
         <v>84.6875</v>
@@ -9103,10 +9103,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>84.741600000000005</v>
+        <v>84.709800000000001</v>
       </c>
       <c r="C11" s="0">
-        <v>20.814</v>
+        <v>20.646999999999998</v>
       </c>
       <c r="D11" s="0">
         <v>84.743200000000002</v>
@@ -9860,10 +9860,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>84.585300000000004</v>
+        <v>84.621799999999993</v>
       </c>
       <c r="C12" s="0">
-        <v>19.799499999999998</v>
+        <v>19.885200000000001</v>
       </c>
       <c r="D12" s="0">
         <v>84.588200000000001</v>
@@ -10617,10 +10617,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>84.414699999999996</v>
+        <v>84.394499999999994</v>
       </c>
       <c r="C13" s="0">
-        <v>19.165500000000002</v>
+        <v>18.666899999999998</v>
       </c>
       <c r="D13" s="0">
         <v>84.416600000000003</v>
@@ -11374,10 +11374,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>84.3142</v>
+        <v>84.3155</v>
       </c>
       <c r="C14" s="0">
-        <v>18.795999999999999</v>
+        <v>18.777999999999999</v>
       </c>
       <c r="D14" s="0">
         <v>84.3155</v>
@@ -12131,10 +12131,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>84.2453</v>
+        <v>84.2363</v>
       </c>
       <c r="C15" s="0">
-        <v>17.443999999999999</v>
+        <v>17.758299999999998</v>
       </c>
       <c r="D15" s="0">
         <v>84.264099999999999</v>
@@ -12888,10 +12888,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>84.197599999999994</v>
+        <v>84.175399999999996</v>
       </c>
       <c r="C16" s="0">
-        <v>17.667300000000001</v>
+        <v>17.206600000000002</v>
       </c>
       <c r="D16" s="0">
         <v>84.209500000000006</v>
@@ -13645,10 +13645,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>84.198499999999996</v>
+        <v>84.198800000000006</v>
       </c>
       <c r="C17" s="0">
-        <v>17.657699999999998</v>
+        <v>17.650099999999998</v>
       </c>
       <c r="D17" s="0">
         <v>84.219999999999999</v>
@@ -14402,10 +14402,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>84.219999999999999</v>
+        <v>84.187899999999999</v>
       </c>
       <c r="C18" s="0">
-        <v>18.117899999999999</v>
+        <v>17.987300000000001</v>
       </c>
       <c r="D18" s="0">
         <v>84.221699999999998</v>
@@ -15159,10 +15159,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>84.187399999999997</v>
+        <v>84.198800000000006</v>
       </c>
       <c r="C19" s="0">
-        <v>17.993400000000001</v>
+        <v>17.650099999999998</v>
       </c>
       <c r="D19" s="0">
         <v>84.190700000000007</v>
@@ -15916,10 +15916,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>84.188400000000001</v>
+        <v>84.210599999999999</v>
       </c>
       <c r="C20" s="0">
-        <v>17.979900000000001</v>
+        <v>18.434999999999999</v>
       </c>
       <c r="D20" s="0">
         <v>84.214100000000002</v>
@@ -16673,10 +16673,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>84.259100000000004</v>
+        <v>84.248000000000005</v>
       </c>
       <c r="C21" s="0">
-        <v>18.211300000000001</v>
+        <v>18.547999999999998</v>
       </c>
       <c r="D21" s="0">
         <v>84.259200000000007</v>
@@ -17430,10 +17430,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>84.304299999999998</v>
+        <v>84.3155</v>
       </c>
       <c r="C22" s="0">
-        <v>19.114799999999999</v>
+        <v>18.777999999999999</v>
       </c>
       <c r="D22" s="0">
         <v>84.307100000000005</v>
@@ -18187,10 +18187,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>84.305300000000003</v>
+        <v>84.292199999999994</v>
       </c>
       <c r="C23" s="0">
-        <v>19.102499999999999</v>
+        <v>19.460000000000001</v>
       </c>
       <c r="D23" s="0">
         <v>84.315600000000003</v>
@@ -18944,10 +18944,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>84.427400000000006</v>
+        <v>84.426400000000001</v>
       </c>
       <c r="C24" s="0">
-        <v>19.945799999999998</v>
+        <v>19.951599999999999</v>
       </c>
       <c r="D24" s="0">
         <v>84.426500000000004</v>
@@ -19701,10 +19701,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>84.477000000000004</v>
+        <v>84.455600000000004</v>
       </c>
       <c r="C25" s="0">
-        <v>21.718299999999999</v>
+        <v>21.250499999999999</v>
       </c>
       <c r="D25" s="0">
         <v>84.475899999999996</v>
@@ -20458,10 +20458,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>84.549599999999998</v>
+        <v>84.552199999999999</v>
       </c>
       <c r="C26" s="0">
-        <v>22.8323</v>
+        <v>23.694199999999999</v>
       </c>
       <c r="D26" s="0">
         <v>84.561400000000006</v>
@@ -21215,10 +21215,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>84.622699999999995</v>
+        <v>84.620800000000003</v>
       </c>
       <c r="C27" s="0">
-        <v>23.984300000000001</v>
+        <v>24.001300000000001</v>
       </c>
       <c r="D27" s="0">
         <v>84.611699999999999</v>
@@ -21972,10 +21972,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>84.658799999999999</v>
+        <v>84.671099999999996</v>
       </c>
       <c r="C28" s="0">
-        <v>24.990600000000001</v>
+        <v>24.667400000000001</v>
       </c>
       <c r="D28" s="0">
         <v>84.671199999999999</v>
@@ -22729,10 +22729,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>84.691199999999995</v>
+        <v>84.705299999999994</v>
       </c>
       <c r="C29" s="0">
-        <v>25.1556</v>
+        <v>25.696999999999999</v>
       </c>
       <c r="D29" s="0">
         <v>84.700999999999993</v>
@@ -23486,10 +23486,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>84.707899999999995</v>
+        <v>84.705299999999994</v>
       </c>
       <c r="C30" s="0">
-        <v>25.674800000000001</v>
+        <v>25.696999999999999</v>
       </c>
       <c r="D30" s="0">
         <v>84.705399999999997</v>
@@ -24243,10 +24243,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>84.708500000000001</v>
+        <v>84.703500000000005</v>
       </c>
       <c r="C31" s="0">
-        <v>25.6663</v>
+        <v>24.8294</v>
       </c>
       <c r="D31" s="0">
         <v>84.716700000000003</v>
@@ -25000,10 +25000,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>84.714799999999997</v>
+        <v>84.729100000000003</v>
       </c>
       <c r="C32" s="0">
-        <v>23.6065</v>
+        <v>23.2498</v>
       </c>
       <c r="D32" s="0">
         <v>84.7149</v>
@@ -25757,10 +25757,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>84.729100000000003</v>
+        <v>84.696299999999994</v>
       </c>
       <c r="C33" s="0">
-        <v>23.2498</v>
+        <v>23.096800000000002</v>
       </c>
       <c r="D33" s="0">
         <v>84.729100000000003</v>
@@ -26514,10 +26514,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>84.747500000000002</v>
+        <v>84.7149</v>
       </c>
       <c r="C34" s="0">
-        <v>23.765999999999998</v>
+        <v>23.607099999999999</v>
       </c>
       <c r="D34" s="0">
         <v>84.747500000000002</v>
@@ -27271,10 +27271,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>84.606399999999994</v>
+        <v>84.606200000000001</v>
       </c>
       <c r="C35" s="0">
-        <v>24.348600000000001</v>
+        <v>24.349399999999999</v>
       </c>
       <c r="D35" s="0">
         <v>84.653400000000005</v>
@@ -28028,10 +28028,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>84.623599999999996</v>
+        <v>84.623800000000003</v>
       </c>
       <c r="C36" s="0">
-        <v>24.854299999999999</v>
+        <v>24.8552</v>
       </c>
       <c r="D36" s="0">
         <v>84.623599999999996</v>
@@ -28785,10 +28785,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>84.570300000000003</v>
+        <v>84.584900000000005</v>
       </c>
       <c r="C37" s="0">
-        <v>24.191099999999999</v>
+        <v>23.846800000000002</v>
       </c>
       <c r="D37" s="0">
         <v>84.570300000000003</v>
@@ -29542,10 +29542,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>84.428700000000006</v>
+        <v>84.445899999999995</v>
       </c>
       <c r="C38" s="0">
-        <v>24.748200000000001</v>
+        <v>25.240500000000001</v>
       </c>
       <c r="D38" s="0">
         <v>84.443399999999997</v>
@@ -30299,10 +30299,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>84.335300000000004</v>
+        <v>84.335400000000007</v>
       </c>
       <c r="C39" s="0">
-        <v>25.914200000000001</v>
+        <v>25.915800000000001</v>
       </c>
       <c r="D39" s="0">
         <v>84.335300000000004</v>
@@ -31056,10 +31056,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>84.220600000000005</v>
+        <v>84.239999999999995</v>
       </c>
       <c r="C40" s="0">
-        <v>26.563700000000001</v>
+        <v>26.245899999999999</v>
       </c>
       <c r="D40" s="0">
         <v>84.223600000000005</v>
@@ -31813,10 +31813,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>84.140799999999999</v>
+        <v>84.124799999999993</v>
       </c>
       <c r="C41" s="0">
-        <v>26.5623</v>
+        <v>26.8781</v>
       </c>
       <c r="D41" s="0">
         <v>84.140799999999999</v>
@@ -32570,10 +32570,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>84.060500000000005</v>
+        <v>84.060599999999994</v>
       </c>
       <c r="C42" s="0">
-        <v>25.790299999999998</v>
+        <v>25.790800000000001</v>
       </c>
       <c r="D42" s="0">
         <v>84.060500000000005</v>
@@ -33327,10 +33327,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>83.9178</v>
+        <v>83.980900000000005</v>
       </c>
       <c r="C43" s="0">
-        <v>26.260300000000001</v>
+        <v>25.801100000000002</v>
       </c>
       <c r="D43" s="0">
         <v>83.948800000000006</v>
@@ -34084,10 +34084,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>83.881699999999995</v>
+        <v>83.834199999999996</v>
       </c>
       <c r="C44" s="0">
-        <v>26.113399999999999</v>
+        <v>26.2666</v>
       </c>
       <c r="D44" s="0">
         <v>83.881699999999995</v>
@@ -34841,10 +34841,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>83.769900000000007</v>
+        <v>83.738100000000003</v>
       </c>
       <c r="C45" s="0">
-        <v>25.974399999999999</v>
+        <v>25.830500000000001</v>
       </c>
       <c r="D45" s="0">
         <v>83.769900000000007</v>
@@ -35598,10 +35598,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>83.592600000000004</v>
+        <v>83.607299999999995</v>
       </c>
       <c r="C46" s="0">
-        <v>24.840399999999999</v>
+        <v>24.5504</v>
       </c>
       <c r="D46" s="0">
         <v>83.6096</v>
@@ -36355,10 +36355,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>83.5809</v>
+        <v>83.566999999999993</v>
       </c>
       <c r="C47" s="0">
-        <v>22.691800000000001</v>
+        <v>22.988700000000001</v>
       </c>
       <c r="D47" s="0">
         <v>83.599699999999999</v>
@@ -37112,10 +37112,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>83.593500000000006</v>
+        <v>83.560199999999995</v>
       </c>
       <c r="C48" s="0">
-        <v>20.667300000000001</v>
+        <v>20.556000000000001</v>
       </c>
       <c r="D48" s="0">
         <v>83.587999999999994</v>
@@ -37869,10 +37869,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>83.572800000000001</v>
+        <v>83.618300000000005</v>
       </c>
       <c r="C49" s="0">
-        <v>20.255700000000001</v>
+        <v>20.0657</v>
       </c>
       <c r="D49" s="0">
         <v>83.605999999999995</v>
@@ -38626,10 +38626,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>83.618399999999994</v>
+        <v>83.618300000000005</v>
       </c>
       <c r="C50" s="0">
-        <v>20.064599999999999</v>
+        <v>20.0657</v>
       </c>
       <c r="D50" s="0">
         <v>83.630499999999998</v>
@@ -39383,10 +39383,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>83.651700000000005</v>
+        <v>83.618300000000005</v>
       </c>
       <c r="C51" s="0">
-        <v>20.176500000000001</v>
+        <v>20.0657</v>
       </c>
       <c r="D51" s="0">
         <v>83.644499999999994</v>
@@ -40140,10 +40140,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>83.772400000000005</v>
+        <v>83.718599999999995</v>
       </c>
       <c r="C52" s="0">
-        <v>20.9404</v>
+        <v>20.402799999999999</v>
       </c>
       <c r="D52" s="0">
         <v>83.706100000000006</v>
@@ -40897,10 +40897,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>83.739400000000003</v>
+        <v>83.751900000000006</v>
       </c>
       <c r="C53" s="0">
-        <v>20.8231</v>
+        <v>20.517499999999998</v>
       </c>
       <c r="D53" s="0">
         <v>83.739400000000003</v>
@@ -41654,10 +41654,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>83.709199999999996</v>
+        <v>83.709500000000006</v>
       </c>
       <c r="C54" s="0">
-        <v>19.677199999999999</v>
+        <v>19.675799999999999</v>
       </c>
       <c r="D54" s="0">
         <v>83.709199999999996</v>
@@ -42411,10 +42411,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>83.522599999999997</v>
+        <v>83.522900000000007</v>
       </c>
       <c r="C55" s="0">
-        <v>20.445699999999999</v>
+        <v>20.444500000000001</v>
       </c>
       <c r="D55" s="0">
         <v>83.522599999999997</v>
@@ -43168,10 +43168,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>83.364500000000007</v>
+        <v>83.397900000000007</v>
       </c>
       <c r="C56" s="0">
-        <v>20.593499999999999</v>
+        <v>20.701899999999998</v>
       </c>
       <c r="D56" s="0">
         <v>83.364500000000007</v>
@@ -43925,10 +43925,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>83.222499999999997</v>
+        <v>83.209699999999998</v>
       </c>
       <c r="C57" s="0">
-        <v>21.126100000000001</v>
+        <v>21.407399999999999</v>
       </c>
       <c r="D57" s="0">
         <v>83.2226</v>
@@ -44682,10 +44682,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>83.223100000000002</v>
+        <v>83.252099999999999</v>
       </c>
       <c r="C58" s="0">
-        <v>21.120699999999999</v>
+        <v>20.556000000000001</v>
       </c>
       <c r="D58" s="0">
         <v>83.235799999999998</v>
@@ -45439,10 +45439,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>83.389200000000002</v>
+        <v>83.410300000000007</v>
       </c>
       <c r="C59" s="0">
-        <v>20.009699999999999</v>
+        <v>20.4099</v>
       </c>
       <c r="D59" s="0">
         <v>83.389200000000002</v>
@@ -46196,10 +46196,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>83.464399999999998</v>
+        <v>83.4255</v>
       </c>
       <c r="C60" s="0">
-        <v>20.9255</v>
+        <v>21.801400000000001</v>
       </c>
       <c r="D60" s="0">
         <v>83.451599999999999</v>
@@ -46953,10 +46953,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>83.504800000000003</v>
+        <v>83.497600000000006</v>
       </c>
       <c r="C61" s="0">
-        <v>21.738600000000002</v>
+        <v>21.037500000000001</v>
       </c>
       <c r="D61" s="0">
         <v>83.504800000000003</v>
@@ -47710,10 +47710,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>83.556399999999996</v>
+        <v>83.491500000000002</v>
       </c>
       <c r="C62" s="0">
-        <v>20.5565</v>
+        <v>22.036200000000001</v>
       </c>
       <c r="D62" s="0">
         <v>83.556399999999996</v>
@@ -48467,10 +48467,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>83.706100000000006</v>
+        <v>83.6601</v>
       </c>
       <c r="C63" s="0">
-        <v>20.707899999999999</v>
+        <v>20.8978</v>
       </c>
       <c r="D63" s="0">
         <v>83.706100000000006</v>
@@ -49224,10 +49224,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>83.8523</v>
+        <v>83.914199999999994</v>
       </c>
       <c r="C64" s="0">
-        <v>20.866700000000002</v>
+        <v>20.3583</v>
       </c>
       <c r="D64" s="0">
         <v>83.8523</v>
@@ -49981,10 +49981,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>84.072500000000005</v>
+        <v>84.001499999999993</v>
       </c>
       <c r="C65" s="0">
-        <v>20.1906</v>
+        <v>21.037500000000001</v>
       </c>
       <c r="D65" s="0">
         <v>84.072500000000005</v>
@@ -50738,10 +50738,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>84.126599999999996</v>
+        <v>84.093500000000006</v>
       </c>
       <c r="C66" s="0">
-        <v>20.761199999999999</v>
+        <v>20.637599999999999</v>
       </c>
       <c r="D66" s="0">
         <v>84.126599999999996</v>
@@ -51495,10 +51495,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>83.949600000000004</v>
+        <v>83.325100000000006</v>
       </c>
       <c r="C67" s="0">
-        <v>22.301400000000001</v>
+        <v>36.684899999999999</v>
       </c>
       <c r="D67" s="0">
         <v>84.047499999999999</v>
@@ -52252,10 +52252,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>83.922399999999996</v>
+        <v>83.494500000000002</v>
       </c>
       <c r="C68" s="0">
-        <v>21.110800000000001</v>
+        <v>32.374200000000002</v>
       </c>
       <c r="D68" s="0">
         <v>83.968299999999999</v>
@@ -53009,10 +53009,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>84.008899999999997</v>
+        <v>84.008700000000005</v>
       </c>
       <c r="C69" s="0">
-        <v>21.800699999999999</v>
+        <v>21.801400000000001</v>
       </c>
       <c r="D69" s="0">
         <v>84.008899999999997</v>
@@ -53766,10 +53766,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>84.101100000000002</v>
+        <v>84.114099999999993</v>
       </c>
       <c r="C70" s="0">
-        <v>21.4102</v>
+        <v>21.087700000000002</v>
       </c>
       <c r="D70" s="0">
         <v>84.080799999999996</v>
@@ -54523,10 +54523,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>83.968000000000004</v>
+        <v>83.852000000000004</v>
       </c>
       <c r="C71" s="0">
-        <v>20.915400000000002</v>
+        <v>22.671299999999999</v>
       </c>
       <c r="D71" s="0">
         <v>83.968000000000004</v>
@@ -55280,10 +55280,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>83.308300000000003</v>
+        <v>83.693399999999997</v>
       </c>
       <c r="C72" s="0">
-        <v>29.562799999999999</v>
+        <v>21.014099999999999</v>
       </c>
       <c r="D72" s="0">
         <v>83.6678</v>
@@ -56037,10 +56037,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="0">
-        <v>83.398899999999998</v>
+        <v>83.141099999999994</v>
       </c>
       <c r="C73" s="0">
-        <v>22.376899999999999</v>
+        <v>27.101800000000001</v>
       </c>
       <c r="D73" s="0">
         <v>83.438500000000005</v>
@@ -56794,10 +56794,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>83.293099999999995</v>
+        <v>83.029200000000003</v>
       </c>
       <c r="C74" s="0">
-        <v>21.345800000000001</v>
+        <v>25.640999999999998</v>
       </c>
       <c r="D74" s="0">
         <v>83.293099999999995</v>
@@ -57551,10 +57551,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="0">
-        <v>83.072400000000002</v>
+        <v>83.252099999999999</v>
       </c>
       <c r="C75" s="0">
-        <v>24.160900000000002</v>
+        <v>20.556000000000001</v>
       </c>
       <c r="D75" s="0">
         <v>83.228700000000003</v>
@@ -58308,10 +58308,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="0">
-        <v>82.840699999999998</v>
+        <v>82.958799999999997</v>
       </c>
       <c r="C76" s="0">
-        <v>23.333600000000001</v>
+        <v>21.855699999999999</v>
       </c>
       <c r="D76" s="0">
         <v>83.121499999999997</v>
@@ -59065,10 +59065,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="0">
-        <v>82.816199999999995</v>
+        <v>82.893799999999999</v>
       </c>
       <c r="C77" s="0">
-        <v>22.319299999999998</v>
+        <v>20.7256</v>
       </c>
       <c r="D77" s="0">
         <v>83.057400000000001</v>
@@ -59822,10 +59822,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="0">
-        <v>82.909700000000001</v>
+        <v>82.839600000000004</v>
       </c>
       <c r="C78" s="0">
-        <v>19.532</v>
+        <v>20.253299999999999</v>
       </c>
       <c r="D78" s="0">
         <v>82.993700000000004</v>
@@ -60579,10 +60579,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="0">
-        <v>82.842699999999994</v>
+        <v>82.982200000000006</v>
       </c>
       <c r="C79" s="0">
-        <v>19.341000000000001</v>
+        <v>17.878699999999998</v>
       </c>
       <c r="D79" s="0">
         <v>82.959999999999994</v>
@@ -61336,10 +61336,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="0">
-        <v>82.960700000000003</v>
+        <v>82.873699999999999</v>
       </c>
       <c r="C80" s="0">
-        <v>15.3935</v>
+        <v>16.699200000000001</v>
       </c>
       <c r="D80" s="0">
         <v>82.819400000000002</v>
@@ -62093,10 +62093,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="0">
-        <v>82.790199999999999</v>
+        <v>82.800899999999999</v>
       </c>
       <c r="C81" s="0">
-        <v>15.9178</v>
+        <v>15.6312</v>
       </c>
       <c r="D81" s="0">
         <v>82.613799999999998</v>
@@ -62850,10 +62850,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="0">
-        <v>82.828000000000003</v>
+        <v>82.580100000000002</v>
       </c>
       <c r="C82" s="0">
-        <v>14.817299999999999</v>
+        <v>18.347200000000001</v>
       </c>
       <c r="D82" s="0">
         <v>82.602400000000003</v>
@@ -63607,10 +63607,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="0">
-        <v>82.914400000000001</v>
+        <v>83.047200000000004</v>
       </c>
       <c r="C83" s="0">
-        <v>14.404400000000001</v>
+        <v>12.5288</v>
       </c>
       <c r="D83" s="0">
         <v>82.568799999999996</v>
@@ -64364,10 +64364,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="0">
-        <v>82.635800000000003</v>
+        <v>82.522199999999998</v>
       </c>
       <c r="C84" s="0">
-        <v>18.791599999999999</v>
+        <v>19.6538</v>
       </c>
       <c r="D84" s="0">
         <v>82.567599999999999</v>
@@ -65121,10 +65121,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="0">
-        <v>83.094999999999999</v>
+        <v>82.557400000000001</v>
       </c>
       <c r="C85" s="0">
-        <v>12.035</v>
+        <v>18.872299999999999</v>
       </c>
       <c r="D85" s="0">
         <v>82.518000000000001</v>
@@ -65878,10 +65878,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="0">
-        <v>83.053200000000004</v>
+        <v>82.4773</v>
       </c>
       <c r="C86" s="0">
-        <v>10.7514</v>
+        <v>17.223400000000002</v>
       </c>
       <c r="D86" s="0">
         <v>82.477999999999994</v>
@@ -66635,10 +66635,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="0">
-        <v>82.497900000000001</v>
+        <v>82.453800000000001</v>
       </c>
       <c r="C87" s="0">
-        <v>16.699999999999999</v>
+        <v>16.882100000000001</v>
       </c>
       <c r="D87" s="0">
         <v>82.487700000000004</v>
@@ -67392,10 +67392,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="0">
-        <v>82.537199999999999</v>
+        <v>82.409400000000005</v>
       </c>
       <c r="C88" s="0">
-        <v>15.6478</v>
+        <v>17.062899999999999</v>
       </c>
       <c r="D88" s="0">
         <v>82.453800000000001</v>
@@ -68149,10 +68149,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="0">
-        <v>82.245099999999994</v>
+        <v>82.342699999999994</v>
       </c>
       <c r="C89" s="0">
-        <v>16.418800000000001</v>
+        <v>15.797599999999999</v>
       </c>
       <c r="D89" s="0">
         <v>82.288700000000006</v>
@@ -68906,10 +68906,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="0">
-        <v>82.230099999999993</v>
+        <v>82.176699999999997</v>
       </c>
       <c r="C90" s="0">
-        <v>15.8367</v>
+        <v>16.270700000000001</v>
       </c>
       <c r="D90" s="0">
         <v>82.210700000000003</v>
@@ -69663,10 +69663,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="0">
-        <v>82.171800000000005</v>
+        <v>82.2059</v>
       </c>
       <c r="C91" s="0">
-        <v>15.44</v>
+        <v>15.51</v>
       </c>
       <c r="D91" s="0">
         <v>82.186700000000002</v>
@@ -70420,10 +70420,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="0">
-        <v>82.268199999999993</v>
+        <v>82.277000000000001</v>
       </c>
       <c r="C92" s="0">
-        <v>14.8116</v>
+        <v>14.553599999999999</v>
       </c>
       <c r="D92" s="0">
         <v>82.268000000000001</v>
@@ -71177,10 +71177,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="0">
-        <v>82.190299999999993</v>
+        <v>82.224599999999995</v>
       </c>
       <c r="C93" s="0">
-        <v>14.9314</v>
+        <v>14.999700000000001</v>
       </c>
       <c r="D93" s="0">
         <v>82.190299999999993</v>
@@ -71934,10 +71934,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="0">
-        <v>82.199399999999997</v>
+        <v>82.190299999999993</v>
       </c>
       <c r="C94" s="0">
-        <v>14.678800000000001</v>
+        <v>14.9314</v>
       </c>
       <c r="D94" s="0">
         <v>82.181100000000001</v>
@@ -72691,10 +72691,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="0">
-        <v>82.074299999999994</v>
+        <v>82.039900000000003</v>
       </c>
       <c r="C95" s="0">
-        <v>13.91</v>
+        <v>13.848000000000001</v>
       </c>
       <c r="D95" s="0">
         <v>82.074299999999994</v>
@@ -73448,10 +73448,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="0">
-        <v>81.918999999999997</v>
+        <v>81.891800000000003</v>
       </c>
       <c r="C96" s="0">
-        <v>13.119999999999999</v>
+        <v>12.8043</v>
       </c>
       <c r="D96" s="0">
         <v>81.918099999999995</v>
@@ -74205,10 +74205,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="0">
-        <v>81.805499999999995</v>
+        <v>81.798199999999994</v>
       </c>
       <c r="C97" s="0">
-        <v>11.9025</v>
+        <v>12.147399999999999</v>
       </c>
       <c r="D97" s="0">
         <v>81.798199999999994</v>
@@ -74962,10 +74962,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="0">
-        <v>81.666899999999998</v>
+        <v>81.6738</v>
       </c>
       <c r="C98" s="0">
-        <v>11.697900000000001</v>
+        <v>11.455500000000001</v>
       </c>
       <c r="D98" s="0">
         <v>81.701300000000003</v>
@@ -75719,10 +75719,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="0">
-        <v>81.606099999999998</v>
+        <v>81.564400000000006</v>
       </c>
       <c r="C99" s="0">
-        <v>11.123200000000001</v>
+        <v>11.309900000000001</v>
       </c>
       <c r="D99" s="0">
         <v>81.5989</v>
@@ -76476,10 +76476,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="0">
-        <v>81.438699999999997</v>
+        <v>81.432100000000005</v>
       </c>
       <c r="C100" s="0">
-        <v>10.6501</v>
+        <v>10.8855</v>
       </c>
       <c r="D100" s="0">
         <v>81.438699999999997</v>
@@ -77233,10 +77233,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="0">
-        <v>81.280600000000007</v>
+        <v>81.287499999999994</v>
       </c>
       <c r="C101" s="0">
-        <v>10.938800000000001</v>
+        <v>10.706799999999999</v>
       </c>
       <c r="D101" s="0">
         <v>81.280600000000007</v>
@@ -77990,10 +77990,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="0">
-        <v>81.082300000000004</v>
+        <v>81.053200000000004</v>
       </c>
       <c r="C102" s="0">
-        <v>11.173299999999999</v>
+        <v>11.129200000000001</v>
       </c>
       <c r="D102" s="0">
         <v>81.082300000000004</v>
@@ -78747,10 +78747,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="0">
-        <v>80.921199999999999</v>
+        <v>80.719300000000004</v>
       </c>
       <c r="C103" s="0">
-        <v>10.9917</v>
+        <v>10.0466</v>
       </c>
       <c r="D103" s="0">
         <v>80.921199999999999</v>
@@ -79504,10 +79504,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="0">
-        <v>80.760400000000004</v>
+        <v>80.335999999999999</v>
       </c>
       <c r="C104" s="0">
-        <v>10.8104</v>
+        <v>9.2166999999999994</v>
       </c>
       <c r="D104" s="0">
         <v>80.760400000000004</v>
@@ -80267,7 +80267,7 @@
   <cols>
     <col min="1" max="1" width="74.5703125" customWidth="true"/>
     <col min="2" max="2" width="6" customWidth="true"/>
-    <col min="3" max="3" width="83.85546875" customWidth="true"/>
+    <col min="3" max="3" width="75.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
